--- a/D2_refereestats.xlsx
+++ b/D2_refereestats.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>Referee</t>
   </si>
@@ -173,6 +173,12 @@
     <t>40</t>
   </si>
   <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
     <t>0</t>
   </si>
   <si>
@@ -191,22 +197,28 @@
     <t>Patrick Alt</t>
   </si>
   <si>
+    <t>Florian Lechner</t>
+  </si>
+  <si>
+    <t>Max Burda</t>
+  </si>
+  <si>
+    <t>Eric-Dominic Weisbach</t>
+  </si>
+  <si>
+    <t>Florian Heft</t>
+  </si>
+  <si>
+    <t>Richard Hempel</t>
+  </si>
+  <si>
     <t>Wolfgang Haslberger</t>
   </si>
   <si>
-    <t>Florian Lechner</t>
-  </si>
-  <si>
-    <t>Florian Heft</t>
-  </si>
-  <si>
-    <t>Max Burda</t>
-  </si>
-  <si>
-    <t>Eric-Dominic Weisbach</t>
-  </si>
-  <si>
-    <t>Richard Hempel</t>
+    <t>Felix Prigan</t>
+  </si>
+  <si>
+    <t>Robin Braun</t>
   </si>
   <si>
     <t>Lukas Benen</t>
@@ -215,48 +227,51 @@
     <t>Lars Erbst</t>
   </si>
   <si>
+    <t>Florian Exner</t>
+  </si>
+  <si>
+    <t>Patrick Schwengers</t>
+  </si>
+  <si>
+    <t>Timo Gerach</t>
+  </si>
+  <si>
     <t>Nicolas Winter</t>
   </si>
   <si>
-    <t>Felix Prigan</t>
-  </si>
-  <si>
-    <t>Florian Exner</t>
-  </si>
-  <si>
-    <t>Robin Braun</t>
-  </si>
-  <si>
-    <t>Patrick Schwengers</t>
+    <t>Frank Willenborg</t>
+  </si>
+  <si>
+    <t>Sven Jablonski</t>
+  </si>
+  <si>
+    <t>Timo Gansloweit</t>
   </si>
   <si>
     <t>Tobias Welz</t>
   </si>
   <si>
+    <t>Martin Petersen</t>
+  </si>
+  <si>
     <t>Sören Storks</t>
   </si>
   <si>
-    <t>Sven Jablonski</t>
-  </si>
-  <si>
-    <t>Frank Willenborg</t>
-  </si>
-  <si>
-    <t>Martin Petersen</t>
-  </si>
-  <si>
-    <t>Timo Gerach</t>
-  </si>
-  <si>
     <t>Harm Osmers</t>
   </si>
   <si>
+    <t>Tobias Reichel</t>
+  </si>
+  <si>
+    <t>Daniel Schlager</t>
+  </si>
+  <si>
+    <t>Robert Hartmann</t>
+  </si>
+  <si>
     <t>Benjamin Brand</t>
   </si>
   <si>
-    <t>Tobias Reichel</t>
-  </si>
-  <si>
     <t>Christian Dingert</t>
   </si>
   <si>
@@ -266,31 +281,28 @@
     <t>Sascha Stegemann</t>
   </si>
   <si>
+    <t>Tobias Stieler</t>
+  </si>
+  <si>
     <t>Daniel Siebert</t>
   </si>
   <si>
-    <t>Daniel Schlager</t>
-  </si>
-  <si>
     <t>Matthias Jöllenbeck</t>
   </si>
   <si>
+    <t>Deniz Aytekin</t>
+  </si>
+  <si>
     <t>Felix Brych</t>
   </si>
   <si>
-    <t>Robert Hartmann</t>
-  </si>
-  <si>
     <t>Bastian Dankert</t>
   </si>
   <si>
-    <t>Timo Gansloweit</t>
-  </si>
-  <si>
-    <t>Tobias Stieler</t>
-  </si>
-  <si>
     <t>Christian Ballweg</t>
+  </si>
+  <si>
+    <t>Robert Schröder</t>
   </si>
 </sst>
 </file>
@@ -385,43 +397,43 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>45.0</v>
+        <v>60.0</v>
       </c>
       <c r="D2" t="n">
-        <v>2445.0</v>
+        <v>3165.0</v>
       </c>
       <c r="E2" t="n">
-        <v>54.333333333333336</v>
+        <v>52.75</v>
       </c>
       <c r="F2" t="n">
-        <v>34650.0</v>
+        <v>43650.0</v>
       </c>
       <c r="G2" t="n">
-        <v>770.0</v>
+        <v>727.5</v>
       </c>
       <c r="H2" t="n">
-        <v>30250.0</v>
+        <v>38950.0</v>
       </c>
       <c r="I2" t="n">
-        <v>672.2222222222222</v>
+        <v>649.1666666666666</v>
       </c>
       <c r="J2" t="n">
-        <v>40.93333333333333</v>
+        <v>39.86666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>37.77777777777778</v>
+        <v>35.55</v>
       </c>
       <c r="L2" t="n">
-        <v>29.866666666666667</v>
+        <v>27.766666666666666</v>
       </c>
       <c r="M2" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.175266903914591</v>
+        <v>2.0808678500986195</v>
       </c>
     </row>
     <row r="3">
@@ -429,43 +441,43 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>20.0</v>
+        <v>19.0</v>
       </c>
       <c r="D3" t="n">
-        <v>1050.0</v>
+        <v>1010.0</v>
       </c>
       <c r="E3" t="n">
-        <v>52.5</v>
+        <v>53.1578947368421</v>
       </c>
       <c r="F3" t="n">
-        <v>15775.0</v>
+        <v>15375.0</v>
       </c>
       <c r="G3" t="n">
-        <v>788.75</v>
+        <v>809.2105263157895</v>
       </c>
       <c r="H3" t="n">
-        <v>9900.0</v>
+        <v>9500.0</v>
       </c>
       <c r="I3" t="n">
-        <v>495.0</v>
+        <v>500.0</v>
       </c>
       <c r="J3" t="n">
-        <v>30.35</v>
+        <v>29.894736842105264</v>
       </c>
       <c r="K3" t="n">
-        <v>43.65</v>
+        <v>44.10526315789474</v>
       </c>
       <c r="L3" t="n">
-        <v>26.3</v>
+        <v>25.842105263157894</v>
       </c>
       <c r="M3" t="n">
         <v>23.0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.234042553191489</v>
+        <v>2.2295805739514347</v>
       </c>
     </row>
     <row r="4">
@@ -473,43 +485,43 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="D4" t="n">
-        <v>525.0</v>
+        <v>645.0</v>
       </c>
       <c r="E4" t="n">
-        <v>58.333333333333336</v>
+        <v>53.75</v>
       </c>
       <c r="F4" t="n">
-        <v>8200.0</v>
+        <v>9100.0</v>
       </c>
       <c r="G4" t="n">
-        <v>911.1111111111111</v>
+        <v>758.3333333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>4600.0</v>
+        <v>5500.0</v>
       </c>
       <c r="I4" t="n">
-        <v>511.1111111111111</v>
+        <v>458.3333333333333</v>
       </c>
       <c r="J4" t="n">
-        <v>53.22222222222222</v>
+        <v>49.166666666666664</v>
       </c>
       <c r="K4" t="n">
-        <v>40.77777777777778</v>
+        <v>41.166666666666664</v>
       </c>
       <c r="L4" t="n">
-        <v>35.666666666666664</v>
+        <v>34.916666666666664</v>
       </c>
       <c r="M4" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4764150943396226</v>
+        <v>2.179054054054054</v>
       </c>
     </row>
     <row r="5">
@@ -517,43 +529,43 @@
         <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C5" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D5" t="n">
-        <v>290.0</v>
+        <v>455.0</v>
       </c>
       <c r="E5" t="n">
-        <v>41.42857142857143</v>
+        <v>45.5</v>
       </c>
       <c r="F5" t="n">
-        <v>3200.0</v>
+        <v>5250.0</v>
       </c>
       <c r="G5" t="n">
-        <v>457.14285714285717</v>
+        <v>525.0</v>
       </c>
       <c r="H5" t="n">
-        <v>2000.0</v>
+        <v>2650.0</v>
       </c>
       <c r="I5" t="n">
-        <v>285.7142857142857</v>
+        <v>265.0</v>
       </c>
       <c r="J5" t="n">
-        <v>54.714285714285715</v>
+        <v>55.7</v>
       </c>
       <c r="K5" t="n">
-        <v>48.714285714285715</v>
+        <v>50.9</v>
       </c>
       <c r="L5" t="n">
-        <v>31.571428571428573</v>
+        <v>37.2</v>
       </c>
       <c r="M5" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5846994535519126</v>
+        <v>1.8127490039840637</v>
       </c>
     </row>
     <row r="6">
@@ -561,43 +573,43 @@
         <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D6" t="n">
-        <v>410.0</v>
+        <v>550.0</v>
       </c>
       <c r="E6" t="n">
-        <v>58.57142857142857</v>
+        <v>55.0</v>
       </c>
       <c r="F6" t="n">
-        <v>5350.0</v>
+        <v>7050.0</v>
       </c>
       <c r="G6" t="n">
-        <v>764.2857142857143</v>
+        <v>705.0</v>
       </c>
       <c r="H6" t="n">
-        <v>2600.0</v>
+        <v>3300.0</v>
       </c>
       <c r="I6" t="n">
-        <v>371.42857142857144</v>
+        <v>330.0</v>
       </c>
       <c r="J6" t="n">
-        <v>54.285714285714285</v>
+        <v>50.9</v>
       </c>
       <c r="K6" t="n">
-        <v>49.42857142857143</v>
+        <v>53.1</v>
       </c>
       <c r="L6" t="n">
-        <v>37.142857142857146</v>
+        <v>37.1</v>
       </c>
       <c r="M6" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5308641975308643</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -605,43 +617,43 @@
         <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="D7" t="n">
-        <v>535.0</v>
+        <v>735.0</v>
       </c>
       <c r="E7" t="n">
-        <v>76.42857142857143</v>
+        <v>73.5</v>
       </c>
       <c r="F7" t="n">
-        <v>9600.0</v>
+        <v>12100.0</v>
       </c>
       <c r="G7" t="n">
-        <v>1371.4285714285713</v>
+        <v>1210.0</v>
       </c>
       <c r="H7" t="n">
-        <v>6950.0</v>
+        <v>9850.0</v>
       </c>
       <c r="I7" t="n">
-        <v>992.8571428571429</v>
+        <v>985.0</v>
       </c>
       <c r="J7" t="n">
-        <v>33.714285714285715</v>
+        <v>39.0</v>
       </c>
       <c r="K7" t="n">
-        <v>37.857142857142854</v>
+        <v>33.1</v>
       </c>
       <c r="L7" t="n">
-        <v>21.285714285714285</v>
+        <v>21.3</v>
       </c>
       <c r="M7" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.092485549132948</v>
+        <v>2.9282868525896415</v>
       </c>
     </row>
     <row r="8">
@@ -649,43 +661,43 @@
         <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D8" t="n">
-        <v>490.0</v>
+        <v>440.0</v>
       </c>
       <c r="E8" t="n">
-        <v>70.0</v>
+        <v>48.888888888888886</v>
       </c>
       <c r="F8" t="n">
-        <v>9500.0</v>
+        <v>3750.0</v>
       </c>
       <c r="G8" t="n">
-        <v>1357.142857142857</v>
+        <v>416.6666666666667</v>
       </c>
       <c r="H8" t="n">
-        <v>5000.0</v>
+        <v>3100.0</v>
       </c>
       <c r="I8" t="n">
-        <v>714.2857142857143</v>
+        <v>344.44444444444446</v>
       </c>
       <c r="J8" t="n">
-        <v>38.42857142857143</v>
+        <v>42.111111111111114</v>
       </c>
       <c r="K8" t="n">
-        <v>45.857142857142854</v>
+        <v>43.0</v>
       </c>
       <c r="L8" t="n">
-        <v>32.857142857142854</v>
+        <v>32.666666666666664</v>
       </c>
       <c r="M8" t="n">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.550724637681159</v>
+        <v>1.9298245614035088</v>
       </c>
     </row>
     <row r="9">
@@ -693,43 +705,43 @@
         <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="D9" t="n">
-        <v>265.0</v>
+        <v>350.0</v>
       </c>
       <c r="E9" t="n">
-        <v>44.166666666666664</v>
+        <v>38.888888888888886</v>
       </c>
       <c r="F9" t="n">
-        <v>2000.0</v>
+        <v>4200.0</v>
       </c>
       <c r="G9" t="n">
-        <v>333.3333333333333</v>
+        <v>466.6666666666667</v>
       </c>
       <c r="H9" t="n">
-        <v>1500.0</v>
+        <v>3700.0</v>
       </c>
       <c r="I9" t="n">
-        <v>250.0</v>
+        <v>411.1111111111111</v>
       </c>
       <c r="J9" t="n">
-        <v>37.0</v>
+        <v>40.333333333333336</v>
       </c>
       <c r="K9" t="n">
-        <v>44.0</v>
+        <v>27.444444444444443</v>
       </c>
       <c r="L9" t="n">
-        <v>30.833333333333332</v>
+        <v>29.88888888888889</v>
       </c>
       <c r="M9" t="n">
-        <v>23.0</v>
+        <v>20.0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.8794326241134751</v>
+        <v>1.9230769230769231</v>
       </c>
     </row>
     <row r="10">
@@ -737,43 +749,43 @@
         <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="D10" t="n">
-        <v>400.0</v>
+        <v>340.0</v>
       </c>
       <c r="E10" t="n">
-        <v>66.66666666666667</v>
+        <v>37.77777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>7500.0</v>
+        <v>2800.0</v>
       </c>
       <c r="G10" t="n">
-        <v>1250.0</v>
+        <v>311.1111111111111</v>
       </c>
       <c r="H10" t="n">
-        <v>6200.0</v>
+        <v>3700.0</v>
       </c>
       <c r="I10" t="n">
-        <v>1033.3333333333333</v>
+        <v>411.1111111111111</v>
       </c>
       <c r="J10" t="n">
-        <v>54.833333333333336</v>
+        <v>43.77777777777778</v>
       </c>
       <c r="K10" t="n">
-        <v>16.0</v>
+        <v>40.44444444444444</v>
       </c>
       <c r="L10" t="n">
-        <v>26.333333333333332</v>
+        <v>30.666666666666668</v>
       </c>
       <c r="M10" t="n">
-        <v>21.0</v>
+        <v>23.0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.053435114503817</v>
+        <v>1.6037735849056605</v>
       </c>
     </row>
     <row r="11">
@@ -781,43 +793,43 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D11" t="n">
-        <v>210.0</v>
+        <v>515.0</v>
       </c>
       <c r="E11" t="n">
-        <v>35.0</v>
+        <v>64.375</v>
       </c>
       <c r="F11" t="n">
-        <v>2400.0</v>
+        <v>8650.0</v>
       </c>
       <c r="G11" t="n">
-        <v>400.0</v>
+        <v>1081.25</v>
       </c>
       <c r="H11" t="n">
-        <v>2000.0</v>
+        <v>6200.0</v>
       </c>
       <c r="I11" t="n">
-        <v>333.3333333333333</v>
+        <v>775.0</v>
       </c>
       <c r="J11" t="n">
-        <v>43.333333333333336</v>
+        <v>55.625</v>
       </c>
       <c r="K11" t="n">
-        <v>25.5</v>
+        <v>28.875</v>
       </c>
       <c r="L11" t="n">
-        <v>29.166666666666668</v>
+        <v>33.375</v>
       </c>
       <c r="M11" t="n">
-        <v>17.0</v>
+        <v>23.0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.9626168224299065</v>
+        <v>2.7688172043010755</v>
       </c>
     </row>
     <row r="12">
@@ -825,43 +837,43 @@
         <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D12" t="n">
-        <v>220.0</v>
+        <v>460.0</v>
       </c>
       <c r="E12" t="n">
-        <v>36.666666666666664</v>
+        <v>57.5</v>
       </c>
       <c r="F12" t="n">
-        <v>1800.0</v>
+        <v>7250.0</v>
       </c>
       <c r="G12" t="n">
-        <v>300.0</v>
+        <v>906.25</v>
       </c>
       <c r="H12" t="n">
-        <v>3000.0</v>
+        <v>6350.0</v>
       </c>
       <c r="I12" t="n">
-        <v>500.0</v>
+        <v>793.75</v>
       </c>
       <c r="J12" t="n">
-        <v>38.333333333333336</v>
+        <v>23.0</v>
       </c>
       <c r="K12" t="n">
-        <v>43.333333333333336</v>
+        <v>33.75</v>
       </c>
       <c r="L12" t="n">
-        <v>33.166666666666664</v>
+        <v>22.0</v>
       </c>
       <c r="M12" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.4864864864864864</v>
+        <v>2.277227722772277</v>
       </c>
     </row>
     <row r="13">
@@ -869,43 +881,43 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D13" t="n">
-        <v>340.0</v>
+        <v>540.0</v>
       </c>
       <c r="E13" t="n">
-        <v>56.666666666666664</v>
+        <v>67.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5450.0</v>
+        <v>10100.0</v>
       </c>
       <c r="G13" t="n">
-        <v>908.3333333333334</v>
+        <v>1262.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4550.0</v>
+        <v>5400.0</v>
       </c>
       <c r="I13" t="n">
-        <v>758.3333333333334</v>
+        <v>675.0</v>
       </c>
       <c r="J13" t="n">
-        <v>23.5</v>
+        <v>38.125</v>
       </c>
       <c r="K13" t="n">
-        <v>34.166666666666664</v>
+        <v>47.0</v>
       </c>
       <c r="L13" t="n">
-        <v>22.166666666666668</v>
+        <v>33.25</v>
       </c>
       <c r="M13" t="n">
-        <v>24.0</v>
+        <v>20.0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.328767123287671</v>
+        <v>3.253012048192771</v>
       </c>
     </row>
     <row r="14">
@@ -913,43 +925,43 @@
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D14" t="n">
-        <v>275.0</v>
+        <v>360.0</v>
       </c>
       <c r="E14" t="n">
-        <v>55.0</v>
+        <v>51.42857142857143</v>
       </c>
       <c r="F14" t="n">
-        <v>3450.0</v>
+        <v>5025.0</v>
       </c>
       <c r="G14" t="n">
-        <v>690.0</v>
+        <v>717.8571428571429</v>
       </c>
       <c r="H14" t="n">
-        <v>3450.0</v>
+        <v>2550.0</v>
       </c>
       <c r="I14" t="n">
-        <v>690.0</v>
+        <v>364.2857142857143</v>
       </c>
       <c r="J14" t="n">
-        <v>45.6</v>
+        <v>33.0</v>
       </c>
       <c r="K14" t="n">
-        <v>40.2</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="L14" t="n">
-        <v>32.4</v>
+        <v>37.285714285714285</v>
       </c>
       <c r="M14" t="n">
-        <v>26.0</v>
+        <v>20.0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.099236641221374</v>
+        <v>2.535211267605634</v>
       </c>
     </row>
     <row r="15">
@@ -957,43 +969,43 @@
         <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="D15" t="n">
-        <v>330.0</v>
+        <v>300.0</v>
       </c>
       <c r="E15" t="n">
-        <v>66.0</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="F15" t="n">
-        <v>4600.0</v>
+        <v>2900.0</v>
       </c>
       <c r="G15" t="n">
-        <v>920.0</v>
+        <v>414.2857142857143</v>
       </c>
       <c r="H15" t="n">
         <v>2800.0</v>
       </c>
       <c r="I15" t="n">
-        <v>560.0</v>
+        <v>400.0</v>
       </c>
       <c r="J15" t="n">
-        <v>54.4</v>
+        <v>37.57142857142857</v>
       </c>
       <c r="K15" t="n">
-        <v>40.8</v>
+        <v>37.42857142857143</v>
       </c>
       <c r="L15" t="n">
-        <v>34.2</v>
+        <v>28.0</v>
       </c>
       <c r="M15" t="n">
-        <v>26.0</v>
+        <v>24.0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.462686567164179</v>
+        <v>1.744186046511628</v>
       </c>
     </row>
     <row r="16">
@@ -1001,43 +1013,43 @@
         <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C16" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="D16" t="n">
-        <v>300.0</v>
+        <v>400.0</v>
       </c>
       <c r="E16" t="n">
-        <v>75.0</v>
+        <v>57.142857142857146</v>
       </c>
       <c r="F16" t="n">
-        <v>6750.0</v>
+        <v>4650.0</v>
       </c>
       <c r="G16" t="n">
-        <v>1687.5</v>
+        <v>664.2857142857143</v>
       </c>
       <c r="H16" t="n">
-        <v>3600.0</v>
+        <v>4650.0</v>
       </c>
       <c r="I16" t="n">
-        <v>900.0</v>
+        <v>664.2857142857143</v>
       </c>
       <c r="J16" t="n">
-        <v>38.5</v>
+        <v>43.285714285714285</v>
       </c>
       <c r="K16" t="n">
-        <v>18.75</v>
+        <v>29.714285714285715</v>
       </c>
       <c r="L16" t="n">
-        <v>17.75</v>
+        <v>33.857142857142854</v>
       </c>
       <c r="M16" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.125</v>
+        <v>2.2857142857142856</v>
       </c>
     </row>
     <row r="17">
@@ -1045,43 +1057,43 @@
         <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="D17" t="n">
-        <v>240.0</v>
+        <v>390.0</v>
       </c>
       <c r="E17" t="n">
-        <v>60.0</v>
+        <v>55.714285714285715</v>
       </c>
       <c r="F17" t="n">
-        <v>3825.0</v>
+        <v>5000.0</v>
       </c>
       <c r="G17" t="n">
-        <v>956.25</v>
+        <v>714.2857142857143</v>
       </c>
       <c r="H17" t="n">
-        <v>1850.0</v>
+        <v>3400.0</v>
       </c>
       <c r="I17" t="n">
-        <v>462.5</v>
+        <v>485.7142857142857</v>
       </c>
       <c r="J17" t="n">
-        <v>37.5</v>
+        <v>41.857142857142854</v>
       </c>
       <c r="K17" t="n">
-        <v>42.25</v>
+        <v>50.57142857142857</v>
       </c>
       <c r="L17" t="n">
-        <v>32.5</v>
+        <v>39.57142857142857</v>
       </c>
       <c r="M17" t="n">
-        <v>19.0</v>
+        <v>26.0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.116883116883117</v>
+        <v>2.074468085106383</v>
       </c>
     </row>
     <row r="18">
@@ -1089,43 +1101,43 @@
         <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D18" t="n">
-        <v>140.0</v>
+        <v>240.0</v>
       </c>
       <c r="E18" t="n">
-        <v>35.0</v>
+        <v>40.0</v>
       </c>
       <c r="F18" t="n">
-        <v>1200.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G18" t="n">
-        <v>300.0</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>1300.0</v>
+        <v>2100.0</v>
       </c>
       <c r="I18" t="n">
-        <v>325.0</v>
+        <v>350.0</v>
       </c>
       <c r="J18" t="n">
-        <v>31.25</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="K18" t="n">
-        <v>31.5</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="L18" t="n">
-        <v>39.25</v>
+        <v>32.0</v>
       </c>
       <c r="M18" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6091954022988506</v>
+        <v>1.8045112781954886</v>
       </c>
     </row>
     <row r="19">
@@ -1133,43 +1145,43 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D19" t="n">
-        <v>190.0</v>
+        <v>365.0</v>
       </c>
       <c r="E19" t="n">
-        <v>47.5</v>
+        <v>60.833333333333336</v>
       </c>
       <c r="F19" t="n">
-        <v>2200.0</v>
+        <v>5000.0</v>
       </c>
       <c r="G19" t="n">
-        <v>550.0</v>
+        <v>833.3333333333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2000.0</v>
+        <v>4200.0</v>
       </c>
       <c r="I19" t="n">
-        <v>500.0</v>
+        <v>700.0</v>
       </c>
       <c r="J19" t="n">
-        <v>46.75</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="K19" t="n">
-        <v>38.25</v>
+        <v>34.666666666666664</v>
       </c>
       <c r="L19" t="n">
-        <v>33.75</v>
+        <v>26.5</v>
       </c>
       <c r="M19" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.0</v>
+        <v>2.4662162162162162</v>
       </c>
     </row>
     <row r="20">
@@ -1177,43 +1189,43 @@
         <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C20" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="D20" t="n">
-        <v>275.0</v>
+        <v>345.0</v>
       </c>
       <c r="E20" t="n">
-        <v>68.75</v>
+        <v>57.5</v>
       </c>
       <c r="F20" t="n">
-        <v>4100.0</v>
+        <v>4900.0</v>
       </c>
       <c r="G20" t="n">
-        <v>1025.0</v>
+        <v>816.6666666666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3400.0</v>
+        <v>5150.0</v>
       </c>
       <c r="I20" t="n">
-        <v>850.0</v>
+        <v>858.3333333333334</v>
       </c>
       <c r="J20" t="n">
-        <v>41.25</v>
+        <v>26.166666666666668</v>
       </c>
       <c r="K20" t="n">
-        <v>40.0</v>
+        <v>31.333333333333332</v>
       </c>
       <c r="L20" t="n">
-        <v>27.75</v>
+        <v>24.666666666666668</v>
       </c>
       <c r="M20" t="n">
-        <v>24.0</v>
+        <v>19.0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.806122448979592</v>
+        <v>2.948717948717949</v>
       </c>
     </row>
     <row r="21">
@@ -1221,43 +1233,43 @@
         <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C21" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D21" t="n">
-        <v>200.0</v>
+        <v>350.0</v>
       </c>
       <c r="E21" t="n">
-        <v>50.0</v>
+        <v>70.0</v>
       </c>
       <c r="F21" t="n">
-        <v>2000.0</v>
+        <v>7350.0</v>
       </c>
       <c r="G21" t="n">
-        <v>500.0</v>
+        <v>1470.0</v>
       </c>
       <c r="H21" t="n">
-        <v>2400.0</v>
+        <v>3600.0</v>
       </c>
       <c r="I21" t="n">
-        <v>600.0</v>
+        <v>720.0</v>
       </c>
       <c r="J21" t="n">
-        <v>31.0</v>
+        <v>43.8</v>
       </c>
       <c r="K21" t="n">
-        <v>20.0</v>
+        <v>30.4</v>
       </c>
       <c r="L21" t="n">
-        <v>16.25</v>
+        <v>27.2</v>
       </c>
       <c r="M21" t="n">
-        <v>22.0</v>
+        <v>24.0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.2222222222222223</v>
+        <v>2.8925619834710745</v>
       </c>
     </row>
     <row r="22">
@@ -1265,43 +1277,43 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C22" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D22" t="n">
-        <v>195.0</v>
+        <v>200.0</v>
       </c>
       <c r="E22" t="n">
-        <v>48.75</v>
+        <v>40.0</v>
       </c>
       <c r="F22" t="n">
-        <v>2550.0</v>
+        <v>1900.0</v>
       </c>
       <c r="G22" t="n">
-        <v>637.5</v>
+        <v>380.0</v>
       </c>
       <c r="H22" t="n">
-        <v>1950.0</v>
+        <v>1700.0</v>
       </c>
       <c r="I22" t="n">
-        <v>487.5</v>
+        <v>340.0</v>
       </c>
       <c r="J22" t="n">
-        <v>53.0</v>
+        <v>41.4</v>
       </c>
       <c r="K22" t="n">
-        <v>61.25</v>
+        <v>29.6</v>
       </c>
       <c r="L22" t="n">
-        <v>44.5</v>
+        <v>26.8</v>
       </c>
       <c r="M22" t="n">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2674418604651163</v>
+        <v>1.9230769230769231</v>
       </c>
     </row>
     <row r="23">
@@ -1309,43 +1321,43 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C23" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D23" t="n">
-        <v>200.0</v>
+        <v>250.0</v>
       </c>
       <c r="E23" t="n">
         <v>50.0</v>
       </c>
       <c r="F23" t="n">
+        <v>2750.0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>550.0</v>
+      </c>
+      <c r="H23" t="n">
         <v>2350.0</v>
       </c>
-      <c r="G23" t="n">
-        <v>587.5</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1950.0</v>
-      </c>
       <c r="I23" t="n">
-        <v>487.5</v>
+        <v>470.0</v>
       </c>
       <c r="J23" t="n">
-        <v>47.5</v>
+        <v>42.0</v>
       </c>
       <c r="K23" t="n">
-        <v>43.75</v>
+        <v>38.8</v>
       </c>
       <c r="L23" t="n">
-        <v>31.25</v>
+        <v>28.8</v>
       </c>
       <c r="M23" t="n">
-        <v>24.0</v>
+        <v>23.0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.0833333333333335</v>
+        <v>2.1739130434782608</v>
       </c>
     </row>
     <row r="24">
@@ -1353,43 +1365,43 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C24" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D24" t="n">
-        <v>150.0</v>
+        <v>275.0</v>
       </c>
       <c r="E24" t="n">
-        <v>50.0</v>
+        <v>68.75</v>
       </c>
       <c r="F24" t="n">
-        <v>1600.0</v>
+        <v>5450.0</v>
       </c>
       <c r="G24" t="n">
-        <v>533.3333333333334</v>
+        <v>1362.5</v>
       </c>
       <c r="H24" t="n">
-        <v>1400.0</v>
+        <v>2600.0</v>
       </c>
       <c r="I24" t="n">
-        <v>466.6666666666667</v>
+        <v>650.0</v>
       </c>
       <c r="J24" t="n">
-        <v>52.0</v>
+        <v>51.5</v>
       </c>
       <c r="K24" t="n">
-        <v>42.666666666666664</v>
+        <v>35.75</v>
       </c>
       <c r="L24" t="n">
-        <v>38.0</v>
+        <v>31.0</v>
       </c>
       <c r="M24" t="n">
-        <v>17.0</v>
+        <v>24.0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.830188679245283</v>
+        <v>2.806122448979592</v>
       </c>
     </row>
     <row r="25">
@@ -1397,43 +1409,43 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C25" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D25" t="n">
-        <v>145.0</v>
+        <v>200.0</v>
       </c>
       <c r="E25" t="n">
-        <v>48.333333333333336</v>
+        <v>50.0</v>
       </c>
       <c r="F25" t="n">
-        <v>2100.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G25" t="n">
-        <v>700.0</v>
+        <v>500.0</v>
       </c>
       <c r="H25" t="n">
         <v>2400.0</v>
       </c>
       <c r="I25" t="n">
-        <v>800.0</v>
+        <v>600.0</v>
       </c>
       <c r="J25" t="n">
-        <v>27.333333333333332</v>
+        <v>31.0</v>
       </c>
       <c r="K25" t="n">
-        <v>34.0</v>
+        <v>20.0</v>
       </c>
       <c r="L25" t="n">
-        <v>30.666666666666668</v>
+        <v>16.25</v>
       </c>
       <c r="M25" t="n">
-        <v>26.0</v>
+        <v>22.0</v>
       </c>
       <c r="N25" t="n">
-        <v>1.8354430379746836</v>
+        <v>2.2222222222222223</v>
       </c>
     </row>
     <row r="26">
@@ -1441,43 +1453,43 @@
         <v>37</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D26" t="n">
-        <v>170.0</v>
+        <v>185.0</v>
       </c>
       <c r="E26" t="n">
-        <v>56.666666666666664</v>
+        <v>46.25</v>
       </c>
       <c r="F26" t="n">
-        <v>2600.0</v>
+        <v>2400.0</v>
       </c>
       <c r="G26" t="n">
-        <v>866.6666666666666</v>
+        <v>600.0</v>
       </c>
       <c r="H26" t="n">
-        <v>2500.0</v>
+        <v>2700.0</v>
       </c>
       <c r="I26" t="n">
-        <v>833.3333333333334</v>
+        <v>675.0</v>
       </c>
       <c r="J26" t="n">
-        <v>22.0</v>
+        <v>28.5</v>
       </c>
       <c r="K26" t="n">
-        <v>34.666666666666664</v>
+        <v>32.5</v>
       </c>
       <c r="L26" t="n">
-        <v>21.333333333333332</v>
+        <v>30.0</v>
       </c>
       <c r="M26" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.5</v>
+        <v>2.010869565217391</v>
       </c>
     </row>
     <row r="27">
@@ -1485,43 +1497,43 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C27" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="D27" t="n">
-        <v>100.0</v>
+        <v>195.0</v>
       </c>
       <c r="E27" t="n">
-        <v>50.0</v>
+        <v>48.75</v>
       </c>
       <c r="F27" t="n">
-        <v>1200.0</v>
+        <v>2550.0</v>
       </c>
       <c r="G27" t="n">
-        <v>600.0</v>
+        <v>637.5</v>
       </c>
       <c r="H27" t="n">
-        <v>800.0</v>
+        <v>1950.0</v>
       </c>
       <c r="I27" t="n">
-        <v>400.0</v>
+        <v>487.5</v>
       </c>
       <c r="J27" t="n">
-        <v>48.5</v>
+        <v>53.0</v>
       </c>
       <c r="K27" t="n">
-        <v>52.0</v>
+        <v>61.25</v>
       </c>
       <c r="L27" t="n">
-        <v>36.0</v>
+        <v>44.5</v>
       </c>
       <c r="M27" t="n">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="N27" t="n">
-        <v>1.8181818181818181</v>
+        <v>2.2674418604651163</v>
       </c>
     </row>
     <row r="28">
@@ -1529,43 +1541,43 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C28" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D28" t="n">
-        <v>50.0</v>
+        <v>185.0</v>
       </c>
       <c r="E28" t="n">
+        <v>61.666666666666664</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2850.0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>950.0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2450.0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>816.6666666666666</v>
+      </c>
+      <c r="J28" t="n">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="K28" t="n">
+        <v>38.666666666666664</v>
+      </c>
+      <c r="L28" t="n">
         <v>25.0</v>
       </c>
-      <c r="F28" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>200.0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="L28" t="n">
-        <v>43.5</v>
-      </c>
       <c r="M28" t="n">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5151515151515151</v>
+        <v>2.466666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -1573,43 +1585,43 @@
         <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C29" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D29" t="n">
-        <v>40.0</v>
+        <v>90.0</v>
       </c>
       <c r="E29" t="n">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="F29" t="n">
-        <v>200.0</v>
+        <v>800.0</v>
       </c>
       <c r="G29" t="n">
-        <v>100.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="H29" t="n">
-        <v>200.0</v>
+        <v>800.0</v>
       </c>
       <c r="I29" t="n">
-        <v>100.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>37.5</v>
+        <v>32.0</v>
       </c>
       <c r="K29" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="L29" t="n">
-        <v>37.5</v>
+        <v>31.0</v>
       </c>
       <c r="M29" t="n">
-        <v>23.0</v>
+        <v>22.0</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8695652173913043</v>
+        <v>1.3235294117647058</v>
       </c>
     </row>
     <row r="30">
@@ -1617,43 +1629,43 @@
         <v>41</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C30" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D30" t="n">
-        <v>110.0</v>
+        <v>200.0</v>
       </c>
       <c r="E30" t="n">
-        <v>55.0</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>1600.0</v>
+        <v>4475.0</v>
       </c>
       <c r="G30" t="n">
-        <v>800.0</v>
+        <v>1491.6666666666667</v>
       </c>
       <c r="H30" t="n">
-        <v>1400.0</v>
+        <v>900.0</v>
       </c>
       <c r="I30" t="n">
-        <v>700.0</v>
+        <v>300.0</v>
       </c>
       <c r="J30" t="n">
-        <v>14.0</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="K30" t="n">
-        <v>8.5</v>
+        <v>47.0</v>
       </c>
       <c r="L30" t="n">
-        <v>8.5</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="M30" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="31">
@@ -1661,43 +1673,43 @@
         <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C31" t="n">
         <v>2.0</v>
       </c>
       <c r="D31" t="n">
-        <v>180.0</v>
+        <v>70.0</v>
       </c>
       <c r="E31" t="n">
-        <v>90.0</v>
+        <v>35.0</v>
       </c>
       <c r="F31" t="n">
-        <v>2900.0</v>
+        <v>500.0</v>
       </c>
       <c r="G31" t="n">
-        <v>1450.0</v>
+        <v>250.0</v>
       </c>
       <c r="H31" t="n">
-        <v>1400.0</v>
+        <v>900.0</v>
       </c>
       <c r="I31" t="n">
-        <v>700.0</v>
+        <v>450.0</v>
       </c>
       <c r="J31" t="n">
-        <v>47.0</v>
+        <v>20.0</v>
       </c>
       <c r="K31" t="n">
-        <v>28.5</v>
+        <v>57.5</v>
       </c>
       <c r="L31" t="n">
-        <v>28.5</v>
+        <v>53.5</v>
       </c>
       <c r="M31" t="n">
-        <v>27.0</v>
+        <v>23.0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.272727272727273</v>
+        <v>1.5217391304347827</v>
       </c>
     </row>
     <row r="32">
@@ -1705,43 +1717,43 @@
         <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C32" t="n">
         <v>2.0</v>
       </c>
       <c r="D32" t="n">
-        <v>165.0</v>
+        <v>50.0</v>
       </c>
       <c r="E32" t="n">
-        <v>82.5</v>
+        <v>25.0</v>
       </c>
       <c r="F32" t="n">
-        <v>3250.0</v>
+        <v>100.0</v>
       </c>
       <c r="G32" t="n">
-        <v>1625.0</v>
+        <v>50.0</v>
       </c>
       <c r="H32" t="n">
-        <v>400.0</v>
+        <v>200.0</v>
       </c>
       <c r="I32" t="n">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
       <c r="J32" t="n">
-        <v>43.0</v>
+        <v>40.5</v>
       </c>
       <c r="K32" t="n">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="L32" t="n">
-        <v>43.0</v>
+        <v>43.5</v>
       </c>
       <c r="M32" t="n">
         <v>16.0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.15625</v>
+        <v>1.5151515151515151</v>
       </c>
     </row>
     <row r="33">
@@ -1749,43 +1761,43 @@
         <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C33" t="n">
         <v>2.0</v>
       </c>
       <c r="D33" t="n">
-        <v>40.0</v>
+        <v>110.0</v>
       </c>
       <c r="E33" t="n">
-        <v>20.0</v>
+        <v>55.0</v>
       </c>
       <c r="F33" t="n">
-        <v>300.0</v>
+        <v>1600.0</v>
       </c>
       <c r="G33" t="n">
-        <v>150.0</v>
+        <v>800.0</v>
       </c>
       <c r="H33" t="n">
-        <v>400.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I33" t="n">
-        <v>200.0</v>
+        <v>700.0</v>
       </c>
       <c r="J33" t="n">
-        <v>20.0</v>
+        <v>14.0</v>
       </c>
       <c r="K33" t="n">
-        <v>21.5</v>
+        <v>8.5</v>
       </c>
       <c r="L33" t="n">
-        <v>20.0</v>
+        <v>8.5</v>
       </c>
       <c r="M33" t="n">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="34">
@@ -1793,7 +1805,7 @@
         <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C34" t="n">
         <v>2.0</v>
@@ -1805,31 +1817,31 @@
         <v>90.0</v>
       </c>
       <c r="F34" t="n">
-        <v>4375.0</v>
+        <v>2900.0</v>
       </c>
       <c r="G34" t="n">
-        <v>2187.5</v>
+        <v>1450.0</v>
       </c>
       <c r="H34" t="n">
-        <v>900.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I34" t="n">
-        <v>450.0</v>
+        <v>700.0</v>
       </c>
       <c r="J34" t="n">
-        <v>33.5</v>
+        <v>47.0</v>
       </c>
       <c r="K34" t="n">
-        <v>30.0</v>
+        <v>28.5</v>
       </c>
       <c r="L34" t="n">
-        <v>30.0</v>
+        <v>28.5</v>
       </c>
       <c r="M34" t="n">
-        <v>17.0</v>
+        <v>27.0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.142857142857143</v>
+        <v>3.272727272727273</v>
       </c>
     </row>
     <row r="35">
@@ -1837,22 +1849,22 @@
         <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C35" t="n">
         <v>2.0</v>
       </c>
       <c r="D35" t="n">
-        <v>60.0</v>
+        <v>165.0</v>
       </c>
       <c r="E35" t="n">
-        <v>30.0</v>
+        <v>82.5</v>
       </c>
       <c r="F35" t="n">
-        <v>400.0</v>
+        <v>3250.0</v>
       </c>
       <c r="G35" t="n">
-        <v>200.0</v>
+        <v>1625.0</v>
       </c>
       <c r="H35" t="n">
         <v>400.0</v>
@@ -1861,19 +1873,19 @@
         <v>200.0</v>
       </c>
       <c r="J35" t="n">
-        <v>71.5</v>
+        <v>43.0</v>
       </c>
       <c r="K35" t="n">
-        <v>51.5</v>
+        <v>58.5</v>
       </c>
       <c r="L35" t="n">
-        <v>51.5</v>
+        <v>43.0</v>
       </c>
       <c r="M35" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.2765957446808511</v>
+        <v>5.15625</v>
       </c>
     </row>
     <row r="36">
@@ -1881,43 +1893,43 @@
         <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C36" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D36" t="n">
-        <v>10.0</v>
+        <v>90.0</v>
       </c>
       <c r="E36" t="n">
-        <v>10.0</v>
+        <v>45.0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0</v>
+        <v>1100.0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0</v>
+        <v>550.0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0</v>
+        <v>800.0</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0</v>
+        <v>29.5</v>
       </c>
       <c r="K36" t="n">
-        <v>81.0</v>
+        <v>8.0</v>
       </c>
       <c r="L36" t="n">
-        <v>81.0</v>
+        <v>8.0</v>
       </c>
       <c r="M36" t="n">
         <v>19.0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.5263157894736842</v>
+        <v>2.3076923076923075</v>
       </c>
     </row>
     <row r="37">
@@ -1925,43 +1937,43 @@
         <v>48</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C37" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>150.0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>400.0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>200.0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="N37" t="n">
         <v>1.0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>60.0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>500.0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>900.0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>48.0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>36.0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.6666666666666667</v>
       </c>
     </row>
     <row r="38">
@@ -1969,43 +1981,43 @@
         <v>49</v>
       </c>
       <c r="B38" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C38" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D38" t="n">
-        <v>30.0</v>
+        <v>60.0</v>
       </c>
       <c r="E38" t="n">
         <v>30.0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="J38" t="n">
-        <v>59.0</v>
+        <v>71.5</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0</v>
+        <v>51.5</v>
       </c>
       <c r="L38" t="n">
-        <v>59.0</v>
+        <v>51.5</v>
       </c>
       <c r="M38" t="n">
-        <v>32.0</v>
+        <v>23.0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.9375</v>
+        <v>1.2765957446808511</v>
       </c>
     </row>
     <row r="39">
@@ -2013,43 +2025,43 @@
         <v>50</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C39" t="n">
         <v>1.0</v>
       </c>
       <c r="D39" t="n">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="E39" t="n">
-        <v>70.0</v>
+        <v>20.0</v>
       </c>
       <c r="F39" t="n">
-        <v>1200.0</v>
+        <v>100.0</v>
       </c>
       <c r="G39" t="n">
-        <v>1200.0</v>
+        <v>100.0</v>
       </c>
       <c r="H39" t="n">
-        <v>1000.0</v>
+        <v>100.0</v>
       </c>
       <c r="I39" t="n">
-        <v>1000.0</v>
+        <v>100.0</v>
       </c>
       <c r="J39" t="n">
-        <v>46.0</v>
+        <v>98.0</v>
       </c>
       <c r="K39" t="n">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="L39" t="n">
-        <v>35.0</v>
+        <v>20.0</v>
       </c>
       <c r="M39" t="n">
-        <v>24.0</v>
+        <v>18.0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.9166666666666665</v>
+        <v>1.1111111111111112</v>
       </c>
     </row>
     <row r="40">
@@ -2057,43 +2069,43 @@
         <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C40" t="n">
         <v>1.0</v>
       </c>
       <c r="D40" t="n">
-        <v>60.0</v>
+        <v>10.0</v>
       </c>
       <c r="E40" t="n">
-        <v>60.0</v>
+        <v>10.0</v>
       </c>
       <c r="F40" t="n">
-        <v>900.0</v>
+        <v>0.0</v>
       </c>
       <c r="G40" t="n">
-        <v>900.0</v>
+        <v>0.0</v>
       </c>
       <c r="H40" t="n">
-        <v>800.0</v>
+        <v>0.0</v>
       </c>
       <c r="I40" t="n">
-        <v>800.0</v>
+        <v>0.0</v>
       </c>
       <c r="J40" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="K40" t="n">
-        <v>4.0</v>
+        <v>81.0</v>
       </c>
       <c r="L40" t="n">
-        <v>4.0</v>
+        <v>81.0</v>
       </c>
       <c r="M40" t="n">
-        <v>25.0</v>
+        <v>19.0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="41">
@@ -2101,43 +2113,131 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C41" t="n">
         <v>1.0</v>
       </c>
       <c r="D41" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>53</v>
+      </c>
+      <c r="B42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D42" t="n">
         <v>50.0</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E42" t="n">
         <v>50.0</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F42" t="n">
         <v>400.0</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G42" t="n">
         <v>400.0</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H42" t="n">
         <v>600.0</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I42" t="n">
         <v>600.0</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>21.0</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>22.0</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L42" t="n">
         <v>21.0</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M42" t="n">
         <v>34.0</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N42" t="n">
         <v>1.4705882352941178</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>96</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="D43" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1000.0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.6923076923076925</v>
       </c>
     </row>
   </sheetData>

--- a/D2_refereestats.xlsx
+++ b/D2_refereestats.xlsx
@@ -182,66 +182,72 @@
     <t>0</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Michael Bacher</t>
   </si>
   <si>
+    <t>Patrick Alt</t>
+  </si>
+  <si>
     <t>Robert Kampka</t>
   </si>
   <si>
+    <t>Max Burda</t>
+  </si>
+  <si>
     <t>Tom Bauer</t>
   </si>
   <si>
-    <t>Patrick Alt</t>
+    <t>Florian Heft</t>
   </si>
   <si>
     <t>Florian Lechner</t>
   </si>
   <si>
-    <t>Max Burda</t>
+    <t>Robin Braun</t>
   </si>
   <si>
     <t>Eric-Dominic Weisbach</t>
   </si>
   <si>
-    <t>Florian Heft</t>
-  </si>
-  <si>
     <t>Richard Hempel</t>
   </si>
   <si>
+    <t>Felix Prigan</t>
+  </si>
+  <si>
     <t>Wolfgang Haslberger</t>
   </si>
   <si>
-    <t>Felix Prigan</t>
-  </si>
-  <si>
-    <t>Robin Braun</t>
+    <t>Lars Erbst</t>
+  </si>
+  <si>
+    <t>Patrick Schwengers</t>
   </si>
   <si>
     <t>Lukas Benen</t>
   </si>
   <si>
-    <t>Lars Erbst</t>
+    <t>Timo Gerach</t>
+  </si>
+  <si>
+    <t>Nicolas Winter</t>
   </si>
   <si>
     <t>Florian Exner</t>
   </si>
   <si>
-    <t>Patrick Schwengers</t>
-  </si>
-  <si>
-    <t>Timo Gerach</t>
-  </si>
-  <si>
-    <t>Nicolas Winter</t>
+    <t>Robert Hartmann</t>
+  </si>
+  <si>
+    <t>Sören Storks</t>
   </si>
   <si>
     <t>Frank Willenborg</t>
   </si>
   <si>
+    <t>Martin Petersen</t>
+  </si>
+  <si>
     <t>Sven Jablonski</t>
   </si>
   <si>
@@ -251,10 +257,7 @@
     <t>Tobias Welz</t>
   </si>
   <si>
-    <t>Martin Petersen</t>
-  </si>
-  <si>
-    <t>Sören Storks</t>
+    <t>Robert Schröder</t>
   </si>
   <si>
     <t>Harm Osmers</t>
@@ -263,10 +266,16 @@
     <t>Tobias Reichel</t>
   </si>
   <si>
+    <t>Tobias Stieler</t>
+  </si>
+  <si>
     <t>Daniel Schlager</t>
   </si>
   <si>
-    <t>Robert Hartmann</t>
+    <t>Deniz Aytekin</t>
+  </si>
+  <si>
+    <t>Patrick Ittrich</t>
   </si>
   <si>
     <t>Benjamin Brand</t>
@@ -281,18 +290,12 @@
     <t>Sascha Stegemann</t>
   </si>
   <si>
-    <t>Tobias Stieler</t>
-  </si>
-  <si>
     <t>Daniel Siebert</t>
   </si>
   <si>
     <t>Matthias Jöllenbeck</t>
   </si>
   <si>
-    <t>Deniz Aytekin</t>
-  </si>
-  <si>
     <t>Felix Brych</t>
   </si>
   <si>
@@ -300,9 +303,6 @@
   </si>
   <si>
     <t>Christian Ballweg</t>
-  </si>
-  <si>
-    <t>Robert Schröder</t>
   </si>
 </sst>
 </file>
@@ -400,40 +400,40 @@
         <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>60.0</v>
+        <v>66.0</v>
       </c>
       <c r="D2" t="n">
-        <v>3165.0</v>
+        <v>3295.0</v>
       </c>
       <c r="E2" t="n">
-        <v>52.75</v>
+        <v>49.92424242424242</v>
       </c>
       <c r="F2" t="n">
-        <v>43650.0</v>
+        <v>43950.0</v>
       </c>
       <c r="G2" t="n">
-        <v>727.5</v>
+        <v>665.9090909090909</v>
       </c>
       <c r="H2" t="n">
-        <v>38950.0</v>
+        <v>39350.0</v>
       </c>
       <c r="I2" t="n">
-        <v>649.1666666666666</v>
+        <v>596.2121212121212</v>
       </c>
       <c r="J2" t="n">
-        <v>39.86666666666667</v>
+        <v>37.666666666666664</v>
       </c>
       <c r="K2" t="n">
-        <v>35.55</v>
+        <v>35.71212121212121</v>
       </c>
       <c r="L2" t="n">
-        <v>27.766666666666666</v>
+        <v>29.21212121212121</v>
       </c>
       <c r="M2" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.0808678500986195</v>
+        <v>2.0066991473812426</v>
       </c>
     </row>
     <row r="3">
@@ -444,40 +444,40 @@
         <v>56</v>
       </c>
       <c r="C3" t="n">
-        <v>19.0</v>
+        <v>14.0</v>
       </c>
       <c r="D3" t="n">
-        <v>1010.0</v>
+        <v>755.0</v>
       </c>
       <c r="E3" t="n">
-        <v>53.1578947368421</v>
+        <v>53.92857142857143</v>
       </c>
       <c r="F3" t="n">
-        <v>15375.0</v>
+        <v>10900.0</v>
       </c>
       <c r="G3" t="n">
-        <v>809.2105263157895</v>
+        <v>778.5714285714286</v>
       </c>
       <c r="H3" t="n">
-        <v>9500.0</v>
+        <v>7300.0</v>
       </c>
       <c r="I3" t="n">
-        <v>500.0</v>
+        <v>521.4285714285714</v>
       </c>
       <c r="J3" t="n">
-        <v>29.894736842105264</v>
+        <v>46.642857142857146</v>
       </c>
       <c r="K3" t="n">
-        <v>44.10526315789474</v>
+        <v>39.214285714285715</v>
       </c>
       <c r="L3" t="n">
-        <v>25.842105263157894</v>
+        <v>32.92857142857143</v>
       </c>
       <c r="M3" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2295805739514347</v>
+        <v>2.163323782234957</v>
       </c>
     </row>
     <row r="4">
@@ -488,40 +488,40 @@
         <v>57</v>
       </c>
       <c r="C4" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="D4" t="n">
-        <v>645.0</v>
+        <v>960.0</v>
       </c>
       <c r="E4" t="n">
-        <v>53.75</v>
+        <v>73.84615384615384</v>
       </c>
       <c r="F4" t="n">
-        <v>9100.0</v>
+        <v>16100.0</v>
       </c>
       <c r="G4" t="n">
-        <v>758.3333333333334</v>
+        <v>1238.4615384615386</v>
       </c>
       <c r="H4" t="n">
-        <v>5500.0</v>
+        <v>12350.0</v>
       </c>
       <c r="I4" t="n">
-        <v>458.3333333333333</v>
+        <v>950.0</v>
       </c>
       <c r="J4" t="n">
-        <v>49.166666666666664</v>
+        <v>41.15384615384615</v>
       </c>
       <c r="K4" t="n">
-        <v>41.166666666666664</v>
+        <v>32.61538461538461</v>
       </c>
       <c r="L4" t="n">
-        <v>34.916666666666664</v>
+        <v>20.076923076923077</v>
       </c>
       <c r="M4" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.179054054054054</v>
+        <v>2.7988338192419824</v>
       </c>
     </row>
     <row r="5">
@@ -532,40 +532,40 @@
         <v>58</v>
       </c>
       <c r="C5" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D5" t="n">
-        <v>455.0</v>
+        <v>550.0</v>
       </c>
       <c r="E5" t="n">
-        <v>45.5</v>
+        <v>45.833333333333336</v>
       </c>
       <c r="F5" t="n">
-        <v>5250.0</v>
+        <v>6350.0</v>
       </c>
       <c r="G5" t="n">
-        <v>525.0</v>
+        <v>529.1666666666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2650.0</v>
+        <v>2850.0</v>
       </c>
       <c r="I5" t="n">
-        <v>265.0</v>
+        <v>237.5</v>
       </c>
       <c r="J5" t="n">
-        <v>55.7</v>
+        <v>54.083333333333336</v>
       </c>
       <c r="K5" t="n">
-        <v>50.9</v>
+        <v>54.833333333333336</v>
       </c>
       <c r="L5" t="n">
-        <v>37.2</v>
+        <v>38.666666666666664</v>
       </c>
       <c r="M5" t="n">
         <v>25.0</v>
       </c>
       <c r="N5" t="n">
-        <v>1.8127490039840637</v>
+        <v>1.8211920529801324</v>
       </c>
     </row>
     <row r="6">
@@ -576,40 +576,40 @@
         <v>59</v>
       </c>
       <c r="C6" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D6" t="n">
-        <v>550.0</v>
+        <v>480.0</v>
       </c>
       <c r="E6" t="n">
-        <v>55.0</v>
+        <v>40.0</v>
       </c>
       <c r="F6" t="n">
-        <v>7050.0</v>
+        <v>5500.0</v>
       </c>
       <c r="G6" t="n">
-        <v>705.0</v>
+        <v>458.3333333333333</v>
       </c>
       <c r="H6" t="n">
-        <v>3300.0</v>
+        <v>5100.0</v>
       </c>
       <c r="I6" t="n">
-        <v>330.0</v>
+        <v>425.0</v>
       </c>
       <c r="J6" t="n">
-        <v>50.9</v>
+        <v>37.25</v>
       </c>
       <c r="K6" t="n">
-        <v>53.1</v>
+        <v>33.916666666666664</v>
       </c>
       <c r="L6" t="n">
-        <v>37.1</v>
+        <v>29.416666666666668</v>
       </c>
       <c r="M6" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.2</v>
+        <v>1.951219512195122</v>
       </c>
     </row>
     <row r="7">
@@ -620,40 +620,40 @@
         <v>60</v>
       </c>
       <c r="C7" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D7" t="n">
-        <v>735.0</v>
+        <v>600.0</v>
       </c>
       <c r="E7" t="n">
-        <v>73.5</v>
+        <v>54.54545454545455</v>
       </c>
       <c r="F7" t="n">
-        <v>12100.0</v>
+        <v>7650.0</v>
       </c>
       <c r="G7" t="n">
-        <v>1210.0</v>
+        <v>695.4545454545455</v>
       </c>
       <c r="H7" t="n">
-        <v>9850.0</v>
+        <v>3900.0</v>
       </c>
       <c r="I7" t="n">
-        <v>985.0</v>
+        <v>354.54545454545456</v>
       </c>
       <c r="J7" t="n">
-        <v>39.0</v>
+        <v>48.90909090909091</v>
       </c>
       <c r="K7" t="n">
-        <v>33.1</v>
+        <v>52.63636363636363</v>
       </c>
       <c r="L7" t="n">
-        <v>21.3</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="M7" t="n">
         <v>25.0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.9282868525896415</v>
+        <v>2.1739130434782608</v>
       </c>
     </row>
     <row r="8">
@@ -664,40 +664,40 @@
         <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="D8" t="n">
-        <v>440.0</v>
+        <v>655.0</v>
       </c>
       <c r="E8" t="n">
-        <v>48.888888888888886</v>
+        <v>59.54545454545455</v>
       </c>
       <c r="F8" t="n">
-        <v>3750.0</v>
+        <v>9950.0</v>
       </c>
       <c r="G8" t="n">
-        <v>416.6666666666667</v>
+        <v>904.5454545454545</v>
       </c>
       <c r="H8" t="n">
-        <v>3100.0</v>
+        <v>7600.0</v>
       </c>
       <c r="I8" t="n">
-        <v>344.44444444444446</v>
+        <v>690.9090909090909</v>
       </c>
       <c r="J8" t="n">
-        <v>42.111111111111114</v>
+        <v>52.09090909090909</v>
       </c>
       <c r="K8" t="n">
-        <v>43.0</v>
+        <v>35.09090909090909</v>
       </c>
       <c r="L8" t="n">
-        <v>32.666666666666664</v>
+        <v>35.90909090909091</v>
       </c>
       <c r="M8" t="n">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="N8" t="n">
-        <v>1.9298245614035088</v>
+        <v>2.5486381322957197</v>
       </c>
     </row>
     <row r="9">
@@ -708,40 +708,40 @@
         <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D9" t="n">
+        <v>480.0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4050.0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>405.0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3500.0</v>
+      </c>
+      <c r="I9" t="n">
         <v>350.0</v>
       </c>
-      <c r="E9" t="n">
-        <v>38.888888888888886</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4200.0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>466.6666666666667</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3700.0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>411.1111111111111</v>
-      </c>
       <c r="J9" t="n">
-        <v>40.333333333333336</v>
+        <v>40.9</v>
       </c>
       <c r="K9" t="n">
-        <v>27.444444444444443</v>
+        <v>46.3</v>
       </c>
       <c r="L9" t="n">
-        <v>29.88888888888889</v>
+        <v>32.4</v>
       </c>
       <c r="M9" t="n">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.9230769230769231</v>
+        <v>1.9047619047619047</v>
       </c>
     </row>
     <row r="10">
@@ -752,40 +752,40 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D10" t="n">
-        <v>340.0</v>
+        <v>470.0</v>
       </c>
       <c r="E10" t="n">
-        <v>37.77777777777778</v>
+        <v>47.0</v>
       </c>
       <c r="F10" t="n">
-        <v>2800.0</v>
+        <v>5100.0</v>
       </c>
       <c r="G10" t="n">
-        <v>311.1111111111111</v>
+        <v>510.0</v>
       </c>
       <c r="H10" t="n">
-        <v>3700.0</v>
+        <v>4600.0</v>
       </c>
       <c r="I10" t="n">
-        <v>411.1111111111111</v>
+        <v>460.0</v>
       </c>
       <c r="J10" t="n">
-        <v>43.77777777777778</v>
+        <v>34.8</v>
       </c>
       <c r="K10" t="n">
-        <v>40.44444444444444</v>
+        <v>40.1</v>
       </c>
       <c r="L10" t="n">
-        <v>30.666666666666668</v>
+        <v>28.0</v>
       </c>
       <c r="M10" t="n">
-        <v>23.0</v>
+        <v>25.0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6037735849056605</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="11">
@@ -796,40 +796,40 @@
         <v>64</v>
       </c>
       <c r="C11" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D11" t="n">
-        <v>515.0</v>
+        <v>410.0</v>
       </c>
       <c r="E11" t="n">
-        <v>64.375</v>
+        <v>41.0</v>
       </c>
       <c r="F11" t="n">
-        <v>8650.0</v>
+        <v>3800.0</v>
       </c>
       <c r="G11" t="n">
-        <v>1081.25</v>
+        <v>380.0</v>
       </c>
       <c r="H11" t="n">
-        <v>6200.0</v>
+        <v>4700.0</v>
       </c>
       <c r="I11" t="n">
-        <v>775.0</v>
+        <v>470.0</v>
       </c>
       <c r="J11" t="n">
-        <v>55.625</v>
+        <v>41.4</v>
       </c>
       <c r="K11" t="n">
-        <v>28.875</v>
+        <v>40.4</v>
       </c>
       <c r="L11" t="n">
-        <v>33.375</v>
+        <v>29.6</v>
       </c>
       <c r="M11" t="n">
         <v>23.0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.7688172043010755</v>
+        <v>1.7446808510638299</v>
       </c>
     </row>
     <row r="12">
@@ -840,40 +840,40 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="D12" t="n">
-        <v>460.0</v>
+        <v>550.0</v>
       </c>
       <c r="E12" t="n">
-        <v>57.5</v>
+        <v>55.0</v>
       </c>
       <c r="F12" t="n">
-        <v>7250.0</v>
+        <v>7950.0</v>
       </c>
       <c r="G12" t="n">
-        <v>906.25</v>
+        <v>795.0</v>
       </c>
       <c r="H12" t="n">
-        <v>6350.0</v>
+        <v>7050.0</v>
       </c>
       <c r="I12" t="n">
-        <v>793.75</v>
+        <v>705.0</v>
       </c>
       <c r="J12" t="n">
-        <v>23.0</v>
+        <v>19.7</v>
       </c>
       <c r="K12" t="n">
-        <v>33.75</v>
+        <v>38.1</v>
       </c>
       <c r="L12" t="n">
-        <v>22.0</v>
+        <v>18.9</v>
       </c>
       <c r="M12" t="n">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.277227722772277</v>
+        <v>2.217741935483871</v>
       </c>
     </row>
     <row r="13">
@@ -884,40 +884,40 @@
         <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="D13" t="n">
-        <v>540.0</v>
+        <v>440.0</v>
       </c>
       <c r="E13" t="n">
-        <v>67.5</v>
+        <v>48.888888888888886</v>
       </c>
       <c r="F13" t="n">
-        <v>10100.0</v>
+        <v>5825.0</v>
       </c>
       <c r="G13" t="n">
-        <v>1262.5</v>
+        <v>647.2222222222222</v>
       </c>
       <c r="H13" t="n">
-        <v>5400.0</v>
+        <v>3050.0</v>
       </c>
       <c r="I13" t="n">
-        <v>675.0</v>
+        <v>338.8888888888889</v>
       </c>
       <c r="J13" t="n">
-        <v>38.125</v>
+        <v>36.55555555555556</v>
       </c>
       <c r="K13" t="n">
-        <v>47.0</v>
+        <v>33.44444444444444</v>
       </c>
       <c r="L13" t="n">
-        <v>33.25</v>
+        <v>34.55555555555556</v>
       </c>
       <c r="M13" t="n">
         <v>20.0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.253012048192771</v>
+        <v>2.3529411764705883</v>
       </c>
     </row>
     <row r="14">
@@ -928,40 +928,40 @@
         <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="D14" t="n">
-        <v>360.0</v>
+        <v>570.0</v>
       </c>
       <c r="E14" t="n">
-        <v>51.42857142857143</v>
+        <v>63.333333333333336</v>
       </c>
       <c r="F14" t="n">
-        <v>5025.0</v>
+        <v>10300.0</v>
       </c>
       <c r="G14" t="n">
-        <v>717.8571428571429</v>
+        <v>1144.4444444444443</v>
       </c>
       <c r="H14" t="n">
-        <v>2550.0</v>
+        <v>5600.0</v>
       </c>
       <c r="I14" t="n">
-        <v>364.2857142857143</v>
+        <v>622.2222222222222</v>
       </c>
       <c r="J14" t="n">
-        <v>33.0</v>
+        <v>34.111111111111114</v>
       </c>
       <c r="K14" t="n">
-        <v>42.857142857142854</v>
+        <v>49.44444444444444</v>
       </c>
       <c r="L14" t="n">
-        <v>37.285714285714285</v>
+        <v>29.77777777777778</v>
       </c>
       <c r="M14" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.535211267605634</v>
+        <v>3.015873015873016</v>
       </c>
     </row>
     <row r="15">
@@ -972,40 +972,40 @@
         <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D15" t="n">
-        <v>300.0</v>
+        <v>430.0</v>
       </c>
       <c r="E15" t="n">
-        <v>42.857142857142854</v>
+        <v>53.75</v>
       </c>
       <c r="F15" t="n">
-        <v>2900.0</v>
+        <v>5300.0</v>
       </c>
       <c r="G15" t="n">
-        <v>414.2857142857143</v>
+        <v>662.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2800.0</v>
+        <v>3800.0</v>
       </c>
       <c r="I15" t="n">
-        <v>400.0</v>
+        <v>475.0</v>
       </c>
       <c r="J15" t="n">
-        <v>37.57142857142857</v>
+        <v>39.25</v>
       </c>
       <c r="K15" t="n">
-        <v>37.42857142857143</v>
+        <v>44.875</v>
       </c>
       <c r="L15" t="n">
-        <v>28.0</v>
+        <v>35.25</v>
       </c>
       <c r="M15" t="n">
-        <v>24.0</v>
+        <v>26.0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.744186046511628</v>
+        <v>2.0283018867924527</v>
       </c>
     </row>
     <row r="16">
@@ -1019,37 +1019,37 @@
         <v>7.0</v>
       </c>
       <c r="D16" t="n">
-        <v>400.0</v>
+        <v>385.0</v>
       </c>
       <c r="E16" t="n">
-        <v>57.142857142857146</v>
+        <v>55.0</v>
       </c>
       <c r="F16" t="n">
-        <v>4650.0</v>
+        <v>5100.0</v>
       </c>
       <c r="G16" t="n">
-        <v>664.2857142857143</v>
+        <v>728.5714285714286</v>
       </c>
       <c r="H16" t="n">
-        <v>4650.0</v>
+        <v>4300.0</v>
       </c>
       <c r="I16" t="n">
-        <v>664.2857142857143</v>
+        <v>614.2857142857143</v>
       </c>
       <c r="J16" t="n">
-        <v>43.285714285714285</v>
+        <v>34.285714285714285</v>
       </c>
       <c r="K16" t="n">
-        <v>29.714285714285715</v>
+        <v>36.285714285714285</v>
       </c>
       <c r="L16" t="n">
-        <v>33.857142857142854</v>
+        <v>24.142857142857142</v>
       </c>
       <c r="M16" t="n">
-        <v>25.0</v>
+        <v>23.0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2857142857142856</v>
+        <v>2.305389221556886</v>
       </c>
     </row>
     <row r="17">
@@ -1063,37 +1063,37 @@
         <v>7.0</v>
       </c>
       <c r="D17" t="n">
-        <v>390.0</v>
+        <v>400.0</v>
       </c>
       <c r="E17" t="n">
-        <v>55.714285714285715</v>
+        <v>57.142857142857146</v>
       </c>
       <c r="F17" t="n">
-        <v>5000.0</v>
+        <v>4650.0</v>
       </c>
       <c r="G17" t="n">
-        <v>714.2857142857143</v>
+        <v>664.2857142857143</v>
       </c>
       <c r="H17" t="n">
-        <v>3400.0</v>
+        <v>4650.0</v>
       </c>
       <c r="I17" t="n">
-        <v>485.7142857142857</v>
+        <v>664.2857142857143</v>
       </c>
       <c r="J17" t="n">
-        <v>41.857142857142854</v>
+        <v>43.285714285714285</v>
       </c>
       <c r="K17" t="n">
-        <v>50.57142857142857</v>
+        <v>29.714285714285715</v>
       </c>
       <c r="L17" t="n">
-        <v>39.57142857142857</v>
+        <v>33.857142857142854</v>
       </c>
       <c r="M17" t="n">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.074468085106383</v>
+        <v>2.2857142857142856</v>
       </c>
     </row>
     <row r="18">
@@ -1104,40 +1104,40 @@
         <v>71</v>
       </c>
       <c r="C18" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D18" t="n">
-        <v>240.0</v>
+        <v>420.0</v>
       </c>
       <c r="E18" t="n">
-        <v>40.0</v>
+        <v>60.0</v>
       </c>
       <c r="F18" t="n">
-        <v>2000.0</v>
+        <v>6250.0</v>
       </c>
       <c r="G18" t="n">
-        <v>333.3333333333333</v>
+        <v>892.8571428571429</v>
       </c>
       <c r="H18" t="n">
-        <v>2100.0</v>
+        <v>5800.0</v>
       </c>
       <c r="I18" t="n">
-        <v>350.0</v>
+        <v>828.5714285714286</v>
       </c>
       <c r="J18" t="n">
-        <v>36.666666666666664</v>
+        <v>29.0</v>
       </c>
       <c r="K18" t="n">
-        <v>34.833333333333336</v>
+        <v>37.0</v>
       </c>
       <c r="L18" t="n">
-        <v>32.0</v>
+        <v>27.714285714285715</v>
       </c>
       <c r="M18" t="n">
-        <v>22.0</v>
+        <v>21.0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8045112781954886</v>
+        <v>2.8378378378378377</v>
       </c>
     </row>
     <row r="19">
@@ -1151,16 +1151,16 @@
         <v>6.0</v>
       </c>
       <c r="D19" t="n">
-        <v>365.0</v>
+        <v>470.0</v>
       </c>
       <c r="E19" t="n">
-        <v>60.833333333333336</v>
+        <v>78.33333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>5000.0</v>
+        <v>10925.0</v>
       </c>
       <c r="G19" t="n">
-        <v>833.3333333333334</v>
+        <v>1820.8333333333333</v>
       </c>
       <c r="H19" t="n">
         <v>4200.0</v>
@@ -1169,19 +1169,19 @@
         <v>700.0</v>
       </c>
       <c r="J19" t="n">
-        <v>38.333333333333336</v>
+        <v>43.5</v>
       </c>
       <c r="K19" t="n">
-        <v>34.666666666666664</v>
+        <v>32.0</v>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="M19" t="n">
         <v>24.0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4662162162162162</v>
+        <v>3.263888888888889</v>
       </c>
     </row>
     <row r="20">
@@ -1195,37 +1195,37 @@
         <v>6.0</v>
       </c>
       <c r="D20" t="n">
-        <v>345.0</v>
+        <v>240.0</v>
       </c>
       <c r="E20" t="n">
-        <v>57.5</v>
+        <v>40.0</v>
       </c>
       <c r="F20" t="n">
-        <v>4900.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G20" t="n">
-        <v>816.6666666666666</v>
+        <v>333.3333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>5150.0</v>
+        <v>2100.0</v>
       </c>
       <c r="I20" t="n">
-        <v>858.3333333333334</v>
+        <v>350.0</v>
       </c>
       <c r="J20" t="n">
-        <v>26.166666666666668</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="K20" t="n">
-        <v>31.333333333333332</v>
+        <v>34.833333333333336</v>
       </c>
       <c r="L20" t="n">
-        <v>24.666666666666668</v>
+        <v>32.0</v>
       </c>
       <c r="M20" t="n">
-        <v>19.0</v>
+        <v>22.0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.948717948717949</v>
+        <v>1.8045112781954886</v>
       </c>
     </row>
     <row r="21">
@@ -1239,37 +1239,37 @@
         <v>5.0</v>
       </c>
       <c r="D21" t="n">
-        <v>350.0</v>
+        <v>190.0</v>
       </c>
       <c r="E21" t="n">
-        <v>70.0</v>
+        <v>38.0</v>
       </c>
       <c r="F21" t="n">
-        <v>7350.0</v>
+        <v>1500.0</v>
       </c>
       <c r="G21" t="n">
-        <v>1470.0</v>
+        <v>300.0</v>
       </c>
       <c r="H21" t="n">
-        <v>3600.0</v>
+        <v>1900.0</v>
       </c>
       <c r="I21" t="n">
-        <v>720.0</v>
+        <v>380.0</v>
       </c>
       <c r="J21" t="n">
-        <v>43.8</v>
+        <v>40.2</v>
       </c>
       <c r="K21" t="n">
-        <v>30.4</v>
+        <v>55.8</v>
       </c>
       <c r="L21" t="n">
-        <v>27.2</v>
+        <v>45.2</v>
       </c>
       <c r="M21" t="n">
-        <v>24.0</v>
+        <v>19.0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8925619834710745</v>
+        <v>1.9387755102040816</v>
       </c>
     </row>
     <row r="22">
@@ -1283,37 +1283,37 @@
         <v>5.0</v>
       </c>
       <c r="D22" t="n">
-        <v>200.0</v>
+        <v>215.0</v>
       </c>
       <c r="E22" t="n">
-        <v>40.0</v>
+        <v>43.0</v>
       </c>
       <c r="F22" t="n">
-        <v>1900.0</v>
+        <v>2550.0</v>
       </c>
       <c r="G22" t="n">
-        <v>380.0</v>
+        <v>510.0</v>
       </c>
       <c r="H22" t="n">
-        <v>1700.0</v>
+        <v>2050.0</v>
       </c>
       <c r="I22" t="n">
-        <v>340.0</v>
+        <v>410.0</v>
       </c>
       <c r="J22" t="n">
-        <v>41.4</v>
+        <v>42.4</v>
       </c>
       <c r="K22" t="n">
-        <v>29.6</v>
+        <v>58.4</v>
       </c>
       <c r="L22" t="n">
-        <v>26.8</v>
+        <v>45.0</v>
       </c>
       <c r="M22" t="n">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="N22" t="n">
-        <v>1.9230769230769231</v>
+        <v>1.9724770642201834</v>
       </c>
     </row>
     <row r="23">
@@ -1327,37 +1327,37 @@
         <v>5.0</v>
       </c>
       <c r="D23" t="n">
-        <v>250.0</v>
+        <v>200.0</v>
       </c>
       <c r="E23" t="n">
-        <v>50.0</v>
+        <v>40.0</v>
       </c>
       <c r="F23" t="n">
-        <v>2750.0</v>
+        <v>1900.0</v>
       </c>
       <c r="G23" t="n">
-        <v>550.0</v>
+        <v>380.0</v>
       </c>
       <c r="H23" t="n">
-        <v>2350.0</v>
+        <v>1700.0</v>
       </c>
       <c r="I23" t="n">
-        <v>470.0</v>
+        <v>340.0</v>
       </c>
       <c r="J23" t="n">
-        <v>42.0</v>
+        <v>41.4</v>
       </c>
       <c r="K23" t="n">
-        <v>38.8</v>
+        <v>29.6</v>
       </c>
       <c r="L23" t="n">
-        <v>28.8</v>
+        <v>26.8</v>
       </c>
       <c r="M23" t="n">
-        <v>23.0</v>
+        <v>20.0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.1739130434782608</v>
+        <v>1.9230769230769231</v>
       </c>
     </row>
     <row r="24">
@@ -1368,40 +1368,40 @@
         <v>77</v>
       </c>
       <c r="C24" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D24" t="n">
-        <v>275.0</v>
+        <v>205.0</v>
       </c>
       <c r="E24" t="n">
-        <v>68.75</v>
+        <v>41.0</v>
       </c>
       <c r="F24" t="n">
-        <v>5450.0</v>
+        <v>2400.0</v>
       </c>
       <c r="G24" t="n">
-        <v>1362.5</v>
+        <v>480.0</v>
       </c>
       <c r="H24" t="n">
-        <v>2600.0</v>
+        <v>2800.0</v>
       </c>
       <c r="I24" t="n">
-        <v>650.0</v>
+        <v>560.0</v>
       </c>
       <c r="J24" t="n">
-        <v>51.5</v>
+        <v>22.8</v>
       </c>
       <c r="K24" t="n">
-        <v>35.75</v>
+        <v>35.0</v>
       </c>
       <c r="L24" t="n">
-        <v>31.0</v>
+        <v>33.0</v>
       </c>
       <c r="M24" t="n">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.806122448979592</v>
+        <v>1.9158878504672898</v>
       </c>
     </row>
     <row r="25">
@@ -1412,40 +1412,40 @@
         <v>78</v>
       </c>
       <c r="C25" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="D25" t="n">
-        <v>200.0</v>
+        <v>250.0</v>
       </c>
       <c r="E25" t="n">
         <v>50.0</v>
       </c>
       <c r="F25" t="n">
-        <v>2000.0</v>
+        <v>2750.0</v>
       </c>
       <c r="G25" t="n">
-        <v>500.0</v>
+        <v>550.0</v>
       </c>
       <c r="H25" t="n">
-        <v>2400.0</v>
+        <v>2350.0</v>
       </c>
       <c r="I25" t="n">
-        <v>600.0</v>
+        <v>470.0</v>
       </c>
       <c r="J25" t="n">
-        <v>31.0</v>
+        <v>42.0</v>
       </c>
       <c r="K25" t="n">
-        <v>20.0</v>
+        <v>38.8</v>
       </c>
       <c r="L25" t="n">
-        <v>16.25</v>
+        <v>28.8</v>
       </c>
       <c r="M25" t="n">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2222222222222223</v>
+        <v>2.1739130434782608</v>
       </c>
     </row>
     <row r="26">
@@ -1459,37 +1459,37 @@
         <v>4.0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.0</v>
+        <v>275.0</v>
       </c>
       <c r="E26" t="n">
-        <v>46.25</v>
+        <v>68.75</v>
       </c>
       <c r="F26" t="n">
-        <v>2400.0</v>
+        <v>5450.0</v>
       </c>
       <c r="G26" t="n">
-        <v>600.0</v>
+        <v>1362.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2700.0</v>
+        <v>2600.0</v>
       </c>
       <c r="I26" t="n">
-        <v>675.0</v>
+        <v>650.0</v>
       </c>
       <c r="J26" t="n">
-        <v>28.5</v>
+        <v>51.5</v>
       </c>
       <c r="K26" t="n">
-        <v>32.5</v>
+        <v>35.75</v>
       </c>
       <c r="L26" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="M26" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.010869565217391</v>
+        <v>2.806122448979592</v>
       </c>
     </row>
     <row r="27">
@@ -1503,37 +1503,37 @@
         <v>4.0</v>
       </c>
       <c r="D27" t="n">
-        <v>195.0</v>
+        <v>200.0</v>
       </c>
       <c r="E27" t="n">
-        <v>48.75</v>
+        <v>50.0</v>
       </c>
       <c r="F27" t="n">
-        <v>2550.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G27" t="n">
-        <v>637.5</v>
+        <v>500.0</v>
       </c>
       <c r="H27" t="n">
-        <v>1950.0</v>
+        <v>2400.0</v>
       </c>
       <c r="I27" t="n">
-        <v>487.5</v>
+        <v>600.0</v>
       </c>
       <c r="J27" t="n">
-        <v>53.0</v>
+        <v>31.0</v>
       </c>
       <c r="K27" t="n">
-        <v>61.25</v>
+        <v>20.0</v>
       </c>
       <c r="L27" t="n">
-        <v>44.5</v>
+        <v>16.25</v>
       </c>
       <c r="M27" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2674418604651163</v>
+        <v>2.2222222222222223</v>
       </c>
     </row>
     <row r="28">
@@ -1544,40 +1544,40 @@
         <v>81</v>
       </c>
       <c r="C28" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D28" t="n">
-        <v>185.0</v>
+        <v>190.0</v>
       </c>
       <c r="E28" t="n">
-        <v>61.666666666666664</v>
+        <v>47.5</v>
       </c>
       <c r="F28" t="n">
-        <v>2850.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G28" t="n">
-        <v>950.0</v>
+        <v>500.0</v>
       </c>
       <c r="H28" t="n">
-        <v>2450.0</v>
+        <v>900.0</v>
       </c>
       <c r="I28" t="n">
-        <v>816.6666666666666</v>
+        <v>225.0</v>
       </c>
       <c r="J28" t="n">
-        <v>33.333333333333336</v>
+        <v>44.25</v>
       </c>
       <c r="K28" t="n">
-        <v>38.666666666666664</v>
+        <v>50.0</v>
       </c>
       <c r="L28" t="n">
-        <v>25.0</v>
+        <v>34.5</v>
       </c>
       <c r="M28" t="n">
         <v>25.0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.466666666666667</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -1591,37 +1591,37 @@
         <v>3.0</v>
       </c>
       <c r="D29" t="n">
-        <v>90.0</v>
+        <v>185.0</v>
       </c>
       <c r="E29" t="n">
-        <v>30.0</v>
+        <v>61.666666666666664</v>
       </c>
       <c r="F29" t="n">
-        <v>800.0</v>
+        <v>2850.0</v>
       </c>
       <c r="G29" t="n">
-        <v>266.6666666666667</v>
+        <v>950.0</v>
       </c>
       <c r="H29" t="n">
-        <v>800.0</v>
+        <v>2450.0</v>
       </c>
       <c r="I29" t="n">
-        <v>266.6666666666667</v>
+        <v>816.6666666666666</v>
       </c>
       <c r="J29" t="n">
-        <v>32.0</v>
+        <v>33.333333333333336</v>
       </c>
       <c r="K29" t="n">
-        <v>14.0</v>
+        <v>38.666666666666664</v>
       </c>
       <c r="L29" t="n">
-        <v>31.0</v>
+        <v>25.0</v>
       </c>
       <c r="M29" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3235294117647058</v>
+        <v>2.466666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -1635,37 +1635,37 @@
         <v>3.0</v>
       </c>
       <c r="D30" t="n">
-        <v>200.0</v>
+        <v>90.0</v>
       </c>
       <c r="E30" t="n">
-        <v>66.66666666666667</v>
+        <v>30.0</v>
       </c>
       <c r="F30" t="n">
-        <v>4475.0</v>
+        <v>800.0</v>
       </c>
       <c r="G30" t="n">
-        <v>1491.6666666666667</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="H30" t="n">
-        <v>900.0</v>
+        <v>800.0</v>
       </c>
       <c r="I30" t="n">
-        <v>300.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="J30" t="n">
-        <v>40.666666666666664</v>
+        <v>32.0</v>
       </c>
       <c r="K30" t="n">
-        <v>47.0</v>
+        <v>14.0</v>
       </c>
       <c r="L30" t="n">
-        <v>38.333333333333336</v>
+        <v>31.0</v>
       </c>
       <c r="M30" t="n">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3333333333333335</v>
+        <v>1.3235294117647058</v>
       </c>
     </row>
     <row r="31">
@@ -1676,40 +1676,40 @@
         <v>84</v>
       </c>
       <c r="C31" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D31" t="n">
-        <v>70.0</v>
+        <v>110.0</v>
       </c>
       <c r="E31" t="n">
-        <v>35.0</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="F31" t="n">
-        <v>500.0</v>
+        <v>1200.0</v>
       </c>
       <c r="G31" t="n">
-        <v>250.0</v>
+        <v>400.0</v>
       </c>
       <c r="H31" t="n">
-        <v>900.0</v>
+        <v>800.0</v>
       </c>
       <c r="I31" t="n">
-        <v>450.0</v>
+        <v>266.6666666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>20.0</v>
+        <v>49.333333333333336</v>
       </c>
       <c r="K31" t="n">
-        <v>57.5</v>
+        <v>29.666666666666668</v>
       </c>
       <c r="L31" t="n">
-        <v>53.5</v>
+        <v>29.666666666666668</v>
       </c>
       <c r="M31" t="n">
-        <v>23.0</v>
+        <v>18.0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.5217391304347827</v>
+        <v>1.9642857142857142</v>
       </c>
     </row>
     <row r="32">
@@ -1720,40 +1720,40 @@
         <v>85</v>
       </c>
       <c r="C32" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D32" t="n">
-        <v>50.0</v>
+        <v>200.0</v>
       </c>
       <c r="E32" t="n">
-        <v>25.0</v>
+        <v>66.66666666666667</v>
       </c>
       <c r="F32" t="n">
-        <v>100.0</v>
+        <v>4475.0</v>
       </c>
       <c r="G32" t="n">
-        <v>50.0</v>
+        <v>1491.6666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>200.0</v>
+        <v>900.0</v>
       </c>
       <c r="I32" t="n">
-        <v>100.0</v>
+        <v>300.0</v>
       </c>
       <c r="J32" t="n">
-        <v>40.5</v>
+        <v>40.666666666666664</v>
       </c>
       <c r="K32" t="n">
-        <v>49.5</v>
+        <v>47.0</v>
       </c>
       <c r="L32" t="n">
-        <v>43.5</v>
+        <v>38.333333333333336</v>
       </c>
       <c r="M32" t="n">
-        <v>16.0</v>
+        <v>20.0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.5151515151515151</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="33">
@@ -1767,37 +1767,37 @@
         <v>2.0</v>
       </c>
       <c r="D33" t="n">
-        <v>110.0</v>
+        <v>40.0</v>
       </c>
       <c r="E33" t="n">
-        <v>55.0</v>
+        <v>20.0</v>
       </c>
       <c r="F33" t="n">
-        <v>1600.0</v>
+        <v>100.0</v>
       </c>
       <c r="G33" t="n">
-        <v>800.0</v>
+        <v>50.0</v>
       </c>
       <c r="H33" t="n">
-        <v>1400.0</v>
+        <v>200.0</v>
       </c>
       <c r="I33" t="n">
-        <v>700.0</v>
+        <v>100.0</v>
       </c>
       <c r="J33" t="n">
-        <v>14.0</v>
+        <v>49.0</v>
       </c>
       <c r="K33" t="n">
-        <v>8.5</v>
+        <v>24.0</v>
       </c>
       <c r="L33" t="n">
-        <v>8.5</v>
+        <v>24.0</v>
       </c>
       <c r="M33" t="n">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="34">
@@ -1811,37 +1811,37 @@
         <v>2.0</v>
       </c>
       <c r="D34" t="n">
-        <v>180.0</v>
+        <v>125.0</v>
       </c>
       <c r="E34" t="n">
-        <v>90.0</v>
+        <v>62.5</v>
       </c>
       <c r="F34" t="n">
-        <v>2900.0</v>
+        <v>2000.0</v>
       </c>
       <c r="G34" t="n">
-        <v>1450.0</v>
+        <v>1000.0</v>
       </c>
       <c r="H34" t="n">
-        <v>1400.0</v>
+        <v>1250.0</v>
       </c>
       <c r="I34" t="n">
-        <v>700.0</v>
+        <v>625.0</v>
       </c>
       <c r="J34" t="n">
-        <v>47.0</v>
+        <v>37.0</v>
       </c>
       <c r="K34" t="n">
-        <v>28.5</v>
+        <v>41.5</v>
       </c>
       <c r="L34" t="n">
-        <v>28.5</v>
+        <v>30.0</v>
       </c>
       <c r="M34" t="n">
-        <v>27.0</v>
+        <v>22.0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.272727272727273</v>
+        <v>2.840909090909091</v>
       </c>
     </row>
     <row r="35">
@@ -1855,37 +1855,37 @@
         <v>2.0</v>
       </c>
       <c r="D35" t="n">
-        <v>165.0</v>
+        <v>50.0</v>
       </c>
       <c r="E35" t="n">
-        <v>82.5</v>
+        <v>25.0</v>
       </c>
       <c r="F35" t="n">
-        <v>3250.0</v>
+        <v>100.0</v>
       </c>
       <c r="G35" t="n">
-        <v>1625.0</v>
+        <v>50.0</v>
       </c>
       <c r="H35" t="n">
-        <v>400.0</v>
+        <v>200.0</v>
       </c>
       <c r="I35" t="n">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
       <c r="J35" t="n">
-        <v>43.0</v>
+        <v>40.5</v>
       </c>
       <c r="K35" t="n">
-        <v>58.5</v>
+        <v>49.5</v>
       </c>
       <c r="L35" t="n">
-        <v>43.0</v>
+        <v>43.5</v>
       </c>
       <c r="M35" t="n">
         <v>16.0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.15625</v>
+        <v>1.5151515151515151</v>
       </c>
     </row>
     <row r="36">
@@ -1899,37 +1899,37 @@
         <v>2.0</v>
       </c>
       <c r="D36" t="n">
-        <v>90.0</v>
+        <v>110.0</v>
       </c>
       <c r="E36" t="n">
-        <v>45.0</v>
+        <v>55.0</v>
       </c>
       <c r="F36" t="n">
-        <v>1100.0</v>
+        <v>1600.0</v>
       </c>
       <c r="G36" t="n">
-        <v>550.0</v>
+        <v>800.0</v>
       </c>
       <c r="H36" t="n">
-        <v>800.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I36" t="n">
-        <v>400.0</v>
+        <v>700.0</v>
       </c>
       <c r="J36" t="n">
-        <v>29.5</v>
+        <v>14.0</v>
       </c>
       <c r="K36" t="n">
-        <v>8.0</v>
+        <v>8.5</v>
       </c>
       <c r="L36" t="n">
-        <v>8.0</v>
+        <v>8.5</v>
       </c>
       <c r="M36" t="n">
-        <v>19.0</v>
+        <v>25.0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.3076923076923075</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="37">
@@ -1943,37 +1943,37 @@
         <v>2.0</v>
       </c>
       <c r="D37" t="n">
-        <v>40.0</v>
+        <v>180.0</v>
       </c>
       <c r="E37" t="n">
-        <v>20.0</v>
+        <v>90.0</v>
       </c>
       <c r="F37" t="n">
-        <v>300.0</v>
+        <v>2900.0</v>
       </c>
       <c r="G37" t="n">
-        <v>150.0</v>
+        <v>1450.0</v>
       </c>
       <c r="H37" t="n">
-        <v>400.0</v>
+        <v>1400.0</v>
       </c>
       <c r="I37" t="n">
-        <v>200.0</v>
+        <v>700.0</v>
       </c>
       <c r="J37" t="n">
-        <v>20.0</v>
+        <v>47.0</v>
       </c>
       <c r="K37" t="n">
-        <v>21.5</v>
+        <v>28.5</v>
       </c>
       <c r="L37" t="n">
-        <v>20.0</v>
+        <v>28.5</v>
       </c>
       <c r="M37" t="n">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.0</v>
+        <v>3.272727272727273</v>
       </c>
     </row>
     <row r="38">
@@ -1987,16 +1987,16 @@
         <v>2.0</v>
       </c>
       <c r="D38" t="n">
-        <v>60.0</v>
+        <v>165.0</v>
       </c>
       <c r="E38" t="n">
-        <v>30.0</v>
+        <v>82.5</v>
       </c>
       <c r="F38" t="n">
-        <v>400.0</v>
+        <v>3250.0</v>
       </c>
       <c r="G38" t="n">
-        <v>200.0</v>
+        <v>1625.0</v>
       </c>
       <c r="H38" t="n">
         <v>400.0</v>
@@ -2005,19 +2005,19 @@
         <v>200.0</v>
       </c>
       <c r="J38" t="n">
-        <v>71.5</v>
+        <v>43.0</v>
       </c>
       <c r="K38" t="n">
-        <v>51.5</v>
+        <v>58.5</v>
       </c>
       <c r="L38" t="n">
-        <v>51.5</v>
+        <v>43.0</v>
       </c>
       <c r="M38" t="n">
-        <v>23.0</v>
+        <v>16.0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.2765957446808511</v>
+        <v>5.15625</v>
       </c>
     </row>
     <row r="39">
@@ -2028,40 +2028,40 @@
         <v>92</v>
       </c>
       <c r="C39" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D39" t="n">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="E39" t="n">
         <v>20.0</v>
       </c>
       <c r="F39" t="n">
-        <v>100.0</v>
+        <v>300.0</v>
       </c>
       <c r="G39" t="n">
-        <v>100.0</v>
+        <v>150.0</v>
       </c>
       <c r="H39" t="n">
-        <v>100.0</v>
+        <v>400.0</v>
       </c>
       <c r="I39" t="n">
-        <v>100.0</v>
+        <v>200.0</v>
       </c>
       <c r="J39" t="n">
-        <v>98.0</v>
+        <v>20.0</v>
       </c>
       <c r="K39" t="n">
-        <v>20.0</v>
+        <v>21.5</v>
       </c>
       <c r="L39" t="n">
         <v>20.0</v>
       </c>
       <c r="M39" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.1111111111111112</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="40">
@@ -2072,40 +2072,40 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D40" t="n">
-        <v>10.0</v>
+        <v>60.0</v>
       </c>
       <c r="E40" t="n">
-        <v>10.0</v>
+        <v>30.0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0</v>
+        <v>400.0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0</v>
+        <v>200.0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.0</v>
+        <v>71.5</v>
       </c>
       <c r="K40" t="n">
-        <v>81.0</v>
+        <v>51.5</v>
       </c>
       <c r="L40" t="n">
-        <v>81.0</v>
+        <v>51.5</v>
       </c>
       <c r="M40" t="n">
-        <v>19.0</v>
+        <v>23.0</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5263157894736842</v>
+        <v>1.2765957446808511</v>
       </c>
     </row>
     <row r="41">
@@ -2119,10 +2119,10 @@
         <v>1.0</v>
       </c>
       <c r="D41" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="E41" t="n">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
       <c r="F41" t="n">
         <v>0.0</v>
@@ -2137,19 +2137,19 @@
         <v>0.0</v>
       </c>
       <c r="J41" t="n">
-        <v>59.0</v>
+        <v>0.0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.0</v>
+        <v>81.0</v>
       </c>
       <c r="L41" t="n">
-        <v>59.0</v>
+        <v>81.0</v>
       </c>
       <c r="M41" t="n">
-        <v>32.0</v>
+        <v>19.0</v>
       </c>
       <c r="N41" t="n">
-        <v>0.9375</v>
+        <v>0.5263157894736842</v>
       </c>
     </row>
     <row r="42">
@@ -2163,37 +2163,37 @@
         <v>1.0</v>
       </c>
       <c r="D42" t="n">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="E42" t="n">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="F42" t="n">
-        <v>400.0</v>
+        <v>0.0</v>
       </c>
       <c r="G42" t="n">
-        <v>400.0</v>
+        <v>0.0</v>
       </c>
       <c r="H42" t="n">
-        <v>600.0</v>
+        <v>0.0</v>
       </c>
       <c r="I42" t="n">
-        <v>600.0</v>
+        <v>0.0</v>
       </c>
       <c r="J42" t="n">
-        <v>21.0</v>
+        <v>59.0</v>
       </c>
       <c r="K42" t="n">
-        <v>22.0</v>
+        <v>0.0</v>
       </c>
       <c r="L42" t="n">
-        <v>21.0</v>
+        <v>59.0</v>
       </c>
       <c r="M42" t="n">
-        <v>34.0</v>
+        <v>32.0</v>
       </c>
       <c r="N42" t="n">
-        <v>1.4705882352941178</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="43">
@@ -2207,37 +2207,37 @@
         <v>1.0</v>
       </c>
       <c r="D43" t="n">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="E43" t="n">
-        <v>70.0</v>
+        <v>50.0</v>
       </c>
       <c r="F43" t="n">
-        <v>1000.0</v>
+        <v>400.0</v>
       </c>
       <c r="G43" t="n">
-        <v>1000.0</v>
+        <v>400.0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0</v>
+        <v>600.0</v>
       </c>
       <c r="J43" t="n">
-        <v>93.0</v>
+        <v>21.0</v>
       </c>
       <c r="K43" t="n">
-        <v>54.0</v>
+        <v>22.0</v>
       </c>
       <c r="L43" t="n">
-        <v>54.0</v>
+        <v>21.0</v>
       </c>
       <c r="M43" t="n">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.6923076923076925</v>
+        <v>1.4705882352941178</v>
       </c>
     </row>
   </sheetData>
